--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_o_higgins.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_o_higgins.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.17205105315222</v>
+      </c>
+      <c r="C2">
         <v>31.0788476849953</v>
-      </c>
-      <c r="C2">
-        <v>27.17205105315222</v>
       </c>
       <c r="D2">
         <v>3.217622513343037</v>
       </c>
       <c r="E2">
-        <v>19.63897073116812</v>
+        <v>17.17023490534035</v>
       </c>
       <c r="F2">
         <v>63.19079436349152</v>
       </c>
       <c r="G2">
-        <v>17.17023490534035</v>
+        <v>19.63897073116812</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>24.59919839679359</v>
+      </c>
+      <c r="C3">
         <v>33.53707414829659</v>
-      </c>
-      <c r="C3">
-        <v>24.59919839679359</v>
       </c>
       <c r="D3">
         <v>2.981774723633104</v>
       </c>
       <c r="E3">
-        <v>21.20770498035737</v>
+        <v>15.55569636294513</v>
       </c>
       <c r="F3">
         <v>63.2365986566975</v>
       </c>
       <c r="G3">
-        <v>15.55569636294513</v>
+        <v>21.20770498035737</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.45131012905749</v>
+      </c>
+      <c r="C4">
         <v>41.35705905357841</v>
-      </c>
-      <c r="C4">
-        <v>28.45131012905749</v>
       </c>
       <c r="D4">
         <v>2.417966903073286</v>
       </c>
       <c r="E4">
+        <v>16.75495163519115</v>
+      </c>
+      <c r="F4">
+        <v>58.88991248272685</v>
+      </c>
+      <c r="G4">
         <v>24.35513588208199</v>
-      </c>
-      <c r="F4">
-        <v>58.88991248272686</v>
-      </c>
-      <c r="G4">
-        <v>16.75495163519116</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.53105909808497</v>
+      </c>
+      <c r="C5">
         <v>36.68062324112842</v>
-      </c>
-      <c r="C5">
-        <v>27.53105909808497</v>
       </c>
       <c r="D5">
         <v>2.72623502994012</v>
       </c>
       <c r="E5">
-        <v>22.33740177227888</v>
+        <v>16.76559103828791</v>
       </c>
       <c r="F5">
         <v>60.89700718943321</v>
       </c>
       <c r="G5">
-        <v>16.76559103828791</v>
+        <v>22.33740177227888</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.62020905923345</v>
+      </c>
+      <c r="C6">
         <v>33.70034843205575</v>
-      </c>
-      <c r="C6">
-        <v>28.62020905923345</v>
       </c>
       <c r="D6">
         <v>2.967328370554177</v>
       </c>
       <c r="E6">
-        <v>20.76160219808526</v>
+        <v>17.63190658137638</v>
       </c>
       <c r="F6">
         <v>61.60649122053836</v>
       </c>
       <c r="G6">
-        <v>17.63190658137638</v>
+        <v>20.76160219808526</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.71117622436166</v>
+      </c>
+      <c r="C7">
         <v>29.00376726663876</v>
-      </c>
-      <c r="C7">
-        <v>29.71117622436166</v>
       </c>
       <c r="D7">
         <v>3.447827969403954</v>
       </c>
       <c r="E7">
-        <v>18.27412506263682</v>
+        <v>18.7198354300182</v>
       </c>
       <c r="F7">
         <v>63.00603950734499</v>
       </c>
       <c r="G7">
-        <v>18.7198354300182</v>
+        <v>18.27412506263682</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.54551275210757</v>
+      </c>
+      <c r="C8">
         <v>35.09230605058158</v>
-      </c>
-      <c r="C8">
-        <v>28.54551275210757</v>
       </c>
       <c r="D8">
         <v>2.849627489736962</v>
       </c>
       <c r="E8">
-        <v>21.44510743747758</v>
+        <v>17.44432488832372</v>
       </c>
       <c r="F8">
         <v>61.11056767419871</v>
       </c>
       <c r="G8">
-        <v>17.44432488832372</v>
+        <v>21.44510743747758</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>33.36561743341404</v>
+      </c>
+      <c r="C9">
         <v>26.24412476855149</v>
-      </c>
-      <c r="C9">
-        <v>33.36561743341404</v>
       </c>
       <c r="D9">
         <v>3.810376641701943</v>
       </c>
       <c r="E9">
-        <v>16.44268351448306</v>
+        <v>20.9044992950331</v>
       </c>
       <c r="F9">
-        <v>62.65281719048384</v>
+        <v>62.65281719048383</v>
       </c>
       <c r="G9">
-        <v>20.90449929503311</v>
+        <v>16.44268351448305</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.20073228516046</v>
+      </c>
+      <c r="C10">
         <v>38.70342451001508</v>
-      </c>
-      <c r="C10">
-        <v>26.20073228516046</v>
       </c>
       <c r="D10">
         <v>2.583750695603784</v>
       </c>
       <c r="E10">
-        <v>23.47025403252139</v>
+        <v>15.88846078495396</v>
       </c>
       <c r="F10">
         <v>60.64128518252465</v>
       </c>
       <c r="G10">
-        <v>15.88846078495396</v>
+        <v>23.47025403252139</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>28.90302613480055</v>
+      </c>
+      <c r="C11">
         <v>33.24736359468134</v>
-      </c>
-      <c r="C11">
-        <v>28.90302613480055</v>
       </c>
       <c r="D11">
         <v>3.00775728322703</v>
       </c>
       <c r="E11">
-        <v>20.50402940760639</v>
+        <v>17.82482680616429</v>
       </c>
       <c r="F11">
         <v>61.67114378622933</v>
       </c>
       <c r="G11">
-        <v>17.82482680616429</v>
+        <v>20.50402940760639</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.00158646218932</v>
+      </c>
+      <c r="C12">
         <v>32.89264939185616</v>
-      </c>
-      <c r="C12">
-        <v>27.00158646218932</v>
       </c>
       <c r="D12">
         <v>3.040192926045016</v>
       </c>
       <c r="E12">
-        <v>20.57150416721788</v>
+        <v>16.88715438550073</v>
       </c>
       <c r="F12">
         <v>62.54134144728138</v>
       </c>
       <c r="G12">
-        <v>16.88715438550073</v>
+        <v>20.57150416721788</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.40592389585749</v>
+      </c>
+      <c r="C13">
         <v>37.33530093812585</v>
-      </c>
-      <c r="C13">
-        <v>27.40592389585749</v>
       </c>
       <c r="D13">
         <v>2.678430265386787</v>
       </c>
       <c r="E13">
-        <v>22.66299827244226</v>
+        <v>16.63574125023994</v>
       </c>
       <c r="F13">
         <v>60.70126047731782</v>
       </c>
       <c r="G13">
-        <v>16.63574125023994</v>
+        <v>22.66299827244226</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.99526934228598</v>
+      </c>
+      <c r="C14">
         <v>39.11948725774455</v>
-      </c>
-      <c r="C14">
-        <v>26.99526934228598</v>
       </c>
       <c r="D14">
         <v>2.556270723620051</v>
       </c>
       <c r="E14">
-        <v>23.54967617472785</v>
+        <v>16.25097606908272</v>
       </c>
       <c r="F14">
         <v>60.19934775618943</v>
       </c>
       <c r="G14">
-        <v>16.25097606908272</v>
+        <v>23.54967617472785</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>25.89897711694611</v>
+      </c>
+      <c r="C15">
         <v>36.44416323948118</v>
-      </c>
-      <c r="C15">
-        <v>25.89897711694611</v>
       </c>
       <c r="D15">
         <v>2.743923611111111</v>
       </c>
       <c r="E15">
-        <v>22.44884702825593</v>
+        <v>15.95323156869113</v>
       </c>
       <c r="F15">
         <v>61.59792140305294</v>
       </c>
       <c r="G15">
-        <v>15.95323156869113</v>
+        <v>22.44884702825593</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>30.12302029350511</v>
+      </c>
+      <c r="C16">
         <v>31.81333849953988</v>
-      </c>
-      <c r="C16">
-        <v>30.12302029350511</v>
       </c>
       <c r="D16">
         <v>3.143335616959732</v>
       </c>
       <c r="E16">
-        <v>19.64558097801705</v>
+        <v>18.60176461791536</v>
       </c>
       <c r="F16">
         <v>61.75265440406759</v>
       </c>
       <c r="G16">
-        <v>18.60176461791536</v>
+        <v>19.64558097801705</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>25.23310283292438</v>
+      </c>
+      <c r="C17">
         <v>26.8659379879545</v>
-      </c>
-      <c r="C17">
-        <v>25.23310283292438</v>
       </c>
       <c r="D17">
         <v>3.722185320491531</v>
       </c>
       <c r="E17">
-        <v>17.66344997506819</v>
+        <v>16.58991581849646</v>
       </c>
       <c r="F17">
         <v>65.74663420643533</v>
       </c>
       <c r="G17">
-        <v>16.58991581849646</v>
+        <v>17.66344997506819</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.69215634837356</v>
+      </c>
+      <c r="C18">
         <v>39.0444648478489</v>
-      </c>
-      <c r="C18">
-        <v>27.69215634837356</v>
       </c>
       <c r="D18">
         <v>2.561182497690434</v>
       </c>
       <c r="E18">
-        <v>23.41685022026432</v>
+        <v>16.60832284455632</v>
       </c>
       <c r="F18">
         <v>59.97482693517935</v>
       </c>
       <c r="G18">
-        <v>16.60832284455632</v>
+        <v>23.41685022026432</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.51733131992587</v>
+      </c>
+      <c r="C19">
         <v>34.97151486031986</v>
-      </c>
-      <c r="C19">
-        <v>27.51733131992587</v>
       </c>
       <c r="D19">
         <v>2.859470068694799</v>
       </c>
       <c r="E19">
-        <v>21.52240949605035</v>
+        <v>16.93490474380095</v>
       </c>
       <c r="F19">
         <v>61.54268576014869</v>
       </c>
       <c r="G19">
-        <v>16.93490474380095</v>
+        <v>21.52240949605035</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>27.29648991784914</v>
+      </c>
+      <c r="C20">
         <v>48.73039581777446</v>
-      </c>
-      <c r="C20">
-        <v>27.29648991784914</v>
       </c>
       <c r="D20">
         <v>2.052107279693486</v>
       </c>
       <c r="E20">
-        <v>27.6834959694527</v>
+        <v>15.50700042426814</v>
       </c>
       <c r="F20">
-        <v>56.80950360627917</v>
+        <v>56.80950360627916</v>
       </c>
       <c r="G20">
-        <v>15.50700042426814</v>
+        <v>27.68349596945269</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>29.00693683826214</v>
+      </c>
+      <c r="C21">
         <v>42.47900693683826</v>
-      </c>
-      <c r="C21">
-        <v>29.00693683826214</v>
       </c>
       <c r="D21">
         <v>2.354103996562097</v>
       </c>
       <c r="E21">
-        <v>24.77113050883543</v>
+        <v>16.9150521609538</v>
       </c>
       <c r="F21">
         <v>58.31381733021077</v>
       </c>
       <c r="G21">
-        <v>16.9150521609538</v>
+        <v>24.77113050883543</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>23.70457604306864</v>
+      </c>
+      <c r="C22">
         <v>40.64602960969044</v>
-      </c>
-      <c r="C22">
-        <v>23.70457604306864</v>
       </c>
       <c r="D22">
         <v>2.460264900662251</v>
       </c>
       <c r="E22">
-        <v>24.73129286518579</v>
+        <v>14.42317535059883</v>
       </c>
       <c r="F22">
         <v>60.84553178421537</v>
       </c>
       <c r="G22">
-        <v>14.42317535059883</v>
+        <v>24.73129286518579</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>31.9854611540209</v>
+      </c>
+      <c r="C23">
         <v>55.6792367105861</v>
-      </c>
-      <c r="C23">
-        <v>31.9854611540209</v>
       </c>
       <c r="D23">
         <v>1.796001631986944</v>
       </c>
       <c r="E23">
-        <v>29.66953153371262</v>
+        <v>17.0439414114514</v>
       </c>
       <c r="F23">
-        <v>53.28652705483597</v>
+        <v>53.28652705483598</v>
       </c>
       <c r="G23">
-        <v>17.0439414114514</v>
+        <v>29.66953153371263</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>25.86076903744659</v>
+      </c>
+      <c r="C24">
         <v>51.52048253329983</v>
-      </c>
-      <c r="C24">
-        <v>25.86076903744659</v>
       </c>
       <c r="D24">
         <v>1.940975609756098</v>
       </c>
       <c r="E24">
-        <v>29.04505525644658</v>
+        <v>14.57920090677245</v>
       </c>
       <c r="F24">
         <v>56.37574383678096</v>
       </c>
       <c r="G24">
-        <v>14.57920090677245</v>
+        <v>29.04505525644658</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.96825215118387</v>
+      </c>
+      <c r="C25">
         <v>32.38318737717742</v>
-      </c>
-      <c r="C25">
-        <v>27.96825215118387</v>
       </c>
       <c r="D25">
         <v>3.088022152830967</v>
       </c>
       <c r="E25">
-        <v>20.1951335594027</v>
+        <v>17.44184662978167</v>
       </c>
       <c r="F25">
         <v>62.36301981081564</v>
       </c>
       <c r="G25">
-        <v>17.44184662978167</v>
+        <v>20.1951335594027</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>28.55013838620396</v>
+      </c>
+      <c r="C26">
         <v>41.67553757717692</v>
-      </c>
-      <c r="C26">
-        <v>28.55013838620396</v>
       </c>
       <c r="D26">
         <v>2.399489144316731</v>
       </c>
       <c r="E26">
-        <v>24.48252141829779</v>
+        <v>16.77193421299481</v>
       </c>
       <c r="F26">
         <v>58.74554436870739</v>
       </c>
       <c r="G26">
-        <v>16.77193421299481</v>
+        <v>24.48252141829779</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.77868318122556</v>
+      </c>
+      <c r="C27">
         <v>34.4320404172099</v>
-      </c>
-      <c r="C27">
-        <v>27.77868318122556</v>
       </c>
       <c r="D27">
         <v>2.904271683824399</v>
       </c>
       <c r="E27">
-        <v>21.22673498605983</v>
+        <v>17.1250596538819</v>
       </c>
       <c r="F27">
         <v>61.64820536005827</v>
       </c>
       <c r="G27">
-        <v>17.1250596538819</v>
+        <v>21.22673498605983</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.9042675893887</v>
+      </c>
+      <c r="C28">
         <v>45.25951557093425</v>
-      </c>
-      <c r="C28">
-        <v>28.9042675893887</v>
       </c>
       <c r="D28">
         <v>2.209480122324159</v>
       </c>
       <c r="E28">
-        <v>25.98675496688742</v>
+        <v>16.59602649006623</v>
       </c>
       <c r="F28">
-        <v>57.41721854304636</v>
+        <v>57.41721854304635</v>
       </c>
       <c r="G28">
-        <v>16.59602649006623</v>
+        <v>25.98675496688741</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>26.81550539744848</v>
+      </c>
+      <c r="C29">
         <v>35.16519463526333</v>
-      </c>
-      <c r="C29">
-        <v>26.81550539744848</v>
       </c>
       <c r="D29">
         <v>2.843720930232558</v>
       </c>
       <c r="E29">
-        <v>21.7094966426011</v>
+        <v>16.5547533700207</v>
       </c>
       <c r="F29">
         <v>61.7357499873782</v>
       </c>
       <c r="G29">
-        <v>16.5547533700207</v>
+        <v>21.7094966426011</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.88852459016394</v>
+      </c>
+      <c r="C30">
         <v>39.97377049180328</v>
-      </c>
-      <c r="C30">
-        <v>25.88852459016394</v>
       </c>
       <c r="D30">
         <v>2.501640419947507</v>
       </c>
       <c r="E30">
+        <v>15.60844469044042</v>
+      </c>
+      <c r="F30">
+        <v>60.29097809757255</v>
+      </c>
+      <c r="G30">
         <v>24.10057721198703</v>
-      </c>
-      <c r="F30">
-        <v>60.29097809757254</v>
-      </c>
-      <c r="G30">
-        <v>15.60844469044042</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>24.4288649824731</v>
+      </c>
+      <c r="C31">
         <v>37.68886739997582</v>
-      </c>
-      <c r="C31">
-        <v>24.4288649824731</v>
       </c>
       <c r="D31">
         <v>2.653303399615138</v>
       </c>
       <c r="E31">
-        <v>23.24783775723233</v>
+        <v>15.06859528780197</v>
       </c>
       <c r="F31">
         <v>61.6835669549657</v>
       </c>
       <c r="G31">
-        <v>15.06859528780197</v>
+        <v>23.24783775723233</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.62068965517241</v>
+      </c>
+      <c r="C32">
         <v>35.67816091954023</v>
-      </c>
-      <c r="C32">
-        <v>26.62068965517241</v>
       </c>
       <c r="D32">
         <v>2.802835051546392</v>
       </c>
       <c r="E32">
-        <v>21.98300283286119</v>
+        <v>16.40226628895184</v>
       </c>
       <c r="F32">
         <v>61.61473087818697</v>
       </c>
       <c r="G32">
-        <v>16.40226628895184</v>
+        <v>21.98300283286119</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>27.48987854251012</v>
+      </c>
+      <c r="C33">
         <v>51.49797570850202</v>
-      </c>
-      <c r="C33">
-        <v>27.48987854251012</v>
       </c>
       <c r="D33">
         <v>1.941823899371069</v>
       </c>
       <c r="E33">
-        <v>28.771771092513</v>
+        <v>15.35851617281158</v>
       </c>
       <c r="F33">
         <v>55.86971273467541</v>
       </c>
       <c r="G33">
-        <v>15.35851617281158</v>
+        <v>28.771771092513</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>26.55094118508753</v>
+      </c>
+      <c r="C34">
         <v>34.67736028711638</v>
-      </c>
-      <c r="C34">
-        <v>26.55094118508753</v>
       </c>
       <c r="D34">
         <v>2.883725842221987</v>
       </c>
       <c r="E34">
+        <v>16.46791595684271</v>
+      </c>
+      <c r="F34">
+        <v>62.02385008517888</v>
+      </c>
+      <c r="G34">
         <v>21.50823395797842</v>
-      </c>
-      <c r="F34">
-        <v>62.02385008517887</v>
-      </c>
-      <c r="G34">
-        <v>16.4679159568427</v>
       </c>
     </row>
   </sheetData>
